--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Syracuse_20251031.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Syracuse_20251031.xlsx
@@ -887,37 +887,37 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JP/Webstaurant</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Monin - Coconut</t>
+          <t>Cup - Espresso (4oz)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>1.65</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>JP/Webstaurant</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cup - Espresso (4oz)</t>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -927,135 +927,139 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DV 53707</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
+          <t>DV - Gummi Sharks</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>14.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Container - Soup (32oz)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>HILLCREST</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>FRZ Fruit - Mango</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Dutch Valley</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Joe Tea - Black Cherry</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DV 53707</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DV - Gummi Sharks</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>2.42</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>14.52</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Container - Soup (32oz)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DV 053115</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>DV - Gummi Bears (12 oz)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>33.96</t>
         </is>
       </c>
     </row>
